--- a/Manuscript_Data/Metallohydrolase_Nature_2026/raw_wetlab_data/250307_singleZn_order1_cowboy_elutantScreen_100uM_4MUPA_and_100uM_suppZn_25C.xlsx
+++ b/Manuscript_Data/Metallohydrolase_Nature_2026/raw_wetlab_data/250307_singleZn_order1_cowboy_elutantScreen_100uM_4MUPA_and_100uM_suppZn_25C.xlsx
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Z:\Users\Baker_Lab\woodbuse\neo2_platereader\zinc_hydrolase_ULTRAop\single_zinc_esterase\250307_singleZn_order1_cowboy_elutantScreen_100uM_4MUPA_and_100uM_suppZn_25C.xpt</t>
+          <t>250307_singleZn_order1_cowboy_elutantScreen_100uM_4MUPA_and_100uM_suppZn_25C.xpt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Z:\Users\Baker_Lab\woodbuse\neo2_platereader\zinc_hydrolase_ULTRAop\single_zinc_esterase\250307_cowboy_screening_1hr.prt</t>
+          <t>250307_cowboy_screening_1hr.prt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
